--- a/Docs/AGENT策划/list.xlsx
+++ b/Docs/AGENT策划/list.xlsx
@@ -25,6 +25,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性类型" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件稀有度" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数值公式" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商贸商品" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旅途事件" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="背包扩容" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能槽位" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="抽卡系统" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="世界地图节点" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="轮回升级" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="游戏设置" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5838,6 +5846,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>收购价</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>出售价</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>利润</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>产地</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Salt</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>食盐</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>必需品</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>盐井</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 基础生活物资</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Rice</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>大米</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>必需品</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>稻田</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 基础粮食</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Tea</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>茶叶</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>茶山</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 高利润商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Silk</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>丝绸</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>蚕桑</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 顶级商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Porcelain</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>瓷器</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>艺术品</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>瓷窑</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 高价商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Tobacco</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>烟草</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>嗜好品</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>烟田</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 稳定需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Wine</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>酒类</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>嗜好品</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>酒坊</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 旅行消耗品</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Medicine</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>药材</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>必需品</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>药铺</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 医商必备</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Thread</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>棉纱</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>原料</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 制作原料</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Iron</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>生铁</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>原料</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>铁矿</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 锻造原料</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Wood</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>原料</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>林场</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 建筑原料</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Jade</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>玉石</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>玉矿</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 顶级奢侈品</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Pearl</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>珍珠</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>珍珠湾</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 女性最爱</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Gold</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>货币</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>金矿</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 硬通货</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Core.Good.Silver</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>白银</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>货币</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>银矿</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 稳定货币</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Core.Good.Incense</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>香料</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>西域</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 香料之路</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Core.Good.Antique</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>古董</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>艺术品</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>167%</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>遗迹</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 鉴定价值</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Core.Good.Horse</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>马匹</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>交通工具</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>草原</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 坐骑交易</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Core.Good.Paper</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>纸张</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>文化品</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>125%</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>造纸坊</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 文人需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Core.Good.Brush</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>毛笔</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>文化品</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>167%</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>笔庄</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 书法用品</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Core.Good.Rope</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>绳索</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>140%</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>麻田</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 旅行必备</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6920,6 +7792,3372 @@
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>[拓展] 拓展设计 - 高闪避</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>持续时间</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>选项数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Sunny</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>晴空万里</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>短暂</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>旅行速度+20%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 好天气</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Rain</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>绵绵细雨</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>旅行速度-20%,疲劳+5</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 雨天影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Storm</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>暴风雨</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>长</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>旅行速度-50%,HP-10,可能中断</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 恶劣天气</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Snow</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>大雪封路</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>冬季</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>长</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>旅行速度-70%,食物消耗+50%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 冬季专属</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Fog</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>大雾弥漫</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>山地</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>遭遇战概率+30%,速度-30%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 视野受阻</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.MountainPath</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>山路崎岖</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>山地</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>速度-30%,可能发现矿石</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 地形影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.RiverCrossing</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>渡河</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>河流</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>支付金币或寻找渡口</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 交通障碍</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.ForestPath</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>林间小道</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>森林</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>遭遇野兽或发现草药</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 自然环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Desert</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沙漠戈壁</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>沙漠</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>长</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>水消耗+100%,有绿洲事件</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 极端环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Robbery</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>路遇劫匪</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>荒野</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>战斗</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>选择战斗或交钱</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 抢劫事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Lost</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>迷路</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>森林/山地</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>长</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>消耗额外时间或求助向导</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 导航挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Starfall</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>流星雨</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>夜间</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>许愿获得临时buff</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 浪漫事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Plague</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>瘟疫蔓延</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>长</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>全队HP-20%或花费金币治疗</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 卫生事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Core.TravelEvent.Festival</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>节日庆典</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>商店打折,经验+50%</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 欢乐事件</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>最大槽位</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>最大重量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>解锁条件</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>费用</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>初始</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>初始</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 初始背包</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>10级</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>500金币</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 第一次扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20级</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1500金币</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 第二次扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30级</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3000金币</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 第三次扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40级</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5000金币</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 第四次扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50级</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8000金币</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 第五次扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60级</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12000金币</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 第六次扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70级</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20000金币</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 第七次扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>完成7次轮回</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>轮回点数:100</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 永久扩容</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>成就:收藏家</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>成就解锁</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 成就奖励</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>槽位ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>技能类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>数量上限</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>解锁条件</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Passive1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>被动技能槽1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>初始</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 初始解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Passive2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>被动技能槽2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>15级解锁</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 中期解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Passive3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>被动技能槽3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35级解锁</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 后期解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Passive4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>被动技能槽4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>完成第一次轮回</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 轮回解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Active1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>主动技能槽1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>初始</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 初始解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Active2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>主动技能槽2</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25级解锁</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 中期解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Ultimate</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>终极技能槽</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>完成第一次轮回</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 轮回解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Passive5</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>被动技能槽5</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>完成5次轮回</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 轮回解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Active3</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>主动技能槽3</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>60级解锁</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 后期解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Core.SkillSlot.Shared1</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>共享技能槽</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>收集10张GR卡</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 特殊解锁</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>卡池ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>单抽价格</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>十连价格</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>保底</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>保底内容</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Novice</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>新手池</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10抽</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>必出R卡</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 新手专属</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Standard</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>标准池</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>10抽</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>必出R卡</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 常驻卡池</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Premium</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>限定池</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10抽</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>必出SR卡</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 限定角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Limited</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>活动池</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20抽</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>必出SSR卡</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 限时活动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Legendary</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>传说池</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50抽</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>必出UR卡</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 顶级卡池</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Weapon</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>武器池</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>15抽</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>必出R武器</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 装备UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Skill</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>技能池</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>15抽</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>必出R技能</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 技能UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Core.Gacha.Event</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>联动池</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>20抽</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>必出SR卡</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 联动活动</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>节点ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>连接节点</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>事件列表</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>特产</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Start</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>出发点</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 旅程起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Village01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>起始村落</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Start,Wild01</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>新手任务,休息恢复</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>基础物资</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 新手区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Wild01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>东郊荒野</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Wilderness</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Village01,Forest01</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>野兽遭遇,随机事件</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>草药</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 危险区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Wild02</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>西山密林</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Wilderness</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Wild01,Dungeon01</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>野兽遭遇,宝藏发现</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>矿石</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 危险区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Forest01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>迷雾森林</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Wild01,Village02</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>迷途,草药采集</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>稀有草药</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 探索区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Forest02</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>古老森林</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Forest01,Mountain01</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>隐藏事件,精灵</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>古董</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 传说区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Village02</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>边境小镇</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Forest01,Market01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>商店,NPC任务</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>特产交易</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 中转区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.City01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>古代王城</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Market01,Market02</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>大型商店,竞技场</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 核心城市</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Market01</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>东市</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Village02,City01</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>日常交易,随机商人</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>生活物资</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 商业区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Market02</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>西市</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>City01,Mountain01</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>珍稀商品,古董商</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>古董</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 高端市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Mountain01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>险峻山路</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Forest02,Market02,Dungeon02</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>山贼,矿石</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>稀有矿石</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 危险区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Mountain02</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>云顶之巅</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Mountain01,Boss01</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>天气事件,试炼</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>天气祝福</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 挑战区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Dungeon01</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>野兽洞穴</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dungeon</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Wild02,Dungeon02</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>连战,宝藏</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>兽皮</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 初级副本</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Dungeon02</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>废弃矿坑</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Dungeon</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Dungeon01,Mountain01</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>连战,高级矿石</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>精铁</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 中级副本</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Boss01</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>魔王城</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Mountain02,Goal</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>最终BOSS</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>传说装备</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 终点前区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Core.Node.Goal</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>旅程终点</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>阶段结算,轮回选择</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 阶段结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Core.Node.Temple</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>古寺</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Shrine</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Forest02,Village02</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>祈福,任务</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>神圣祝福</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 宗教区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Core.Node.Ruins</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>遗迹</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Ruins</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Mountain02,Dungeon02</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>考古,陷阱</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>古代遗物</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 危险区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Core.Node.Harbor</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Harbor</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>City01,ShipRoute</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>船只交易,坐骑</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>海产</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 水路</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Core.Node.ShipRoute</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>航线</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Harbor,Goal</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>海上事件,海盗</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>海外珍宝</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 水路</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>升级ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>等级上限</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>每次消耗</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.MaxHp</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>生命力强化</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Vitality</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10点</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>+5%最大HP</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 永久加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.Attack</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>攻击力强化</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>10点</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>+5%攻击力</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 永久加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.Defense</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>防御力强化</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10点</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>+5%防御力</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 永久加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.Speed</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>速度强化</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10点</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>+5%速度</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 永久加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.StartingGold</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>起始资金</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20点</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>+100初始金币</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 经济加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.MaxSlot</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>背包扩容</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50点</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>+10背包槽位</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 容量加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.OfflineRate</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>离线收益</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30点</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>+20%离线收益</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 离线加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.TradeDiscount</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>交易折扣</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25点</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>+5%交易折扣</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 交易加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.ExpRate</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>经验加成</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25点</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>+10%经验获取</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 成长加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Prestige.CritRate</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30点</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>+3%暴击率</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战斗加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Core.Prestige.GoldDrop</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>金币掉落</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>40点</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>+15%金币掉落</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Core.Prestige.ItemFind</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>物品发现</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>35点</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>+10%稀有物品概率</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Core.Prestige.SkillSlot</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>技能槽位</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>100点</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>+1被动技能槽</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 稀有升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Core.Prestige.AutoPotion</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>自动喝药</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>QualityOfLife</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>200点</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>HP&lt;30%自动使用药水</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 便利功能</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>设置ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>范围</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.MusicVolume</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>音乐音量</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>背景音乐音量</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 音量控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.SfxVolume</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>音效音量</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>音效音量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 音量控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.ShowDamage</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>显示伤害</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>战斗中显示伤害数字</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] UI设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.AutoSave</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>自动存档</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>每5分钟自动存档</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 存档设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.SaveInterval</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>存档间隔</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>秒</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>自动存档间隔(秒)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 存档设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.SkipBattleAnimation</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>跳过战斗动画</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>快速结束战斗</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战斗设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.AutoEquipment</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>自动装备</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>自动穿戴更好装备</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战斗设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.AutoUsePotion</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>自动喝药</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>HP低时自动使用药水</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战斗设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.PotionThreshold</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>喝药阈值</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>自动喝药的HP百分比</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战斗设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.TravelSpeed</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>旅行速度</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0.5-3.0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>旅行速度倍率</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 旅行设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Setting.ShowTravelTime</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>显示旅行时间</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>显示预计到达时间</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 旅行设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Core.Setting.ShowDamageFloat</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>伤害飘字</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>伤害数字飘动效果</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - UI优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Core.Setting.ConfirmBeforeExit</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>退出确认</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>退出前二次确认</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 误触保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Core.Setting.FastCollectReward</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>快速领取</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>true/false</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>离线奖励一键领取</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 便利功能</t>
         </is>
       </c>
     </row>

--- a/Docs/AGENT策划/list.xlsx
+++ b/Docs/AGENT策划/list.xlsx
@@ -33,6 +33,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="世界地图节点" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="轮回升级" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="游戏设置" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华药材" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华矿石" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华状态效果" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华怪物" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华武器" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华防具" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华事件树详细" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商贸商品详细" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中华地名" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,7 +65,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8BFD8"/>
+        <bgColor rgb="00D8BFD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +122,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11166,6 +11184,2426 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>稀有度</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>售价</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.Ginseng</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>人参</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>上品药材</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>恢复30HP,短暂内攻击+5%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 补气养血</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.Lingzhi</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>灵芝</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>上品药材</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>恢复20HP,防御+10%持续3回合</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 仙草</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Core.Herb.SnowLotus</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>天山雪莲</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>极品药材</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>解除所有debuff,HP全满</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 雪山珍品</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.Cordyceps</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>冬虫夏草</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>上品药材</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>恢复40HP,速度+15%持续2回合</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 滋补圣品</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.Honey</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>蜂蜜</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>普通药材</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>恢复15HP,攻击力+5%持续1回合</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 天然甜味</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.GojiBerry</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>枸杞</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>普通药材</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>恢复10HP,暴击率+3%持续2回合</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 养生佳品</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.Rehmania</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>熟地黄</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>普通药材</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>恢复25HP,持续恢复5HP/秒持续10秒</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 补血药材</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.Saffron</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>藏红花</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>上品药材</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>恢复15HP,全体治疗10HP</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 活血化瘀</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Herb.Licorice</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>甘草</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>普通药材</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>恢复10HP,所有治疗效果+10%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 百搭药材</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Pill.SmallRecovery</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>小还丹</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>下品丹药</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>恢复50HP</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 入门丹药</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Pill.LargeRecovery</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>大还丹</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>中品丹药</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>恢复150HP</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 进阶丹药</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Pill.Xiaoyao</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>逍遥丹</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>上品丹药</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>恢复100HP,解除中毒</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 解毒神药</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Core.Pill.ReturnSoul</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>返魂香</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>极品丹药</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>死亡时复活,恢复50%HP</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 救命仙丹</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Core.Pill.NineTurn</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>九转还魂丹</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>神品丹药</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>HP全满,所有属性+20%持续5回合</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>传说</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 至高神药</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Core.Herb.HeShouWu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>何首乌</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>上品药材</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>永久最大HP+5</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 乌发益精</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Core.Herb.WuWeiZi</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>五味子</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>普通药材</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>恢复20HP,内力+30</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 五味俱全</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Core.Herb.DongZhi</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>天冬</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>普通药材</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>恢复15HP,闪避率+5%持续2回合</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 滋阴润燥</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Core.Herb.ChuanXiong</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>川芎</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>普通药材</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>恢复10HP,攻击速度+10%</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 活血行气</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>售价</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>产地</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.IronOre</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>铁矿石</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>锻造基础装备</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>铁矿</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 最常见矿石</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.CopperOre</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>铜矿石</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>锻造青铜装备</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>铜矿</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 初级金属</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.SilverOre</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>银矿石</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>锻造银器/货币</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>银矿</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 贵金属</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.GoldOre</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>金矿石</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>锻造金器/货币</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>金矿</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 贵金属</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.Soapstone</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>羊脂玉</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>顶级饰品材料</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>玉矿</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 温润如脂</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.HetianJade</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>和田玉</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>传说饰品材料</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>新疆和田</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 玉中上品</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.LapisLazuli</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>蓝纹玉</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>高级饰品材料</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>昆仑山</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 蓝色纹理</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.TianheStone</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>天河石</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>中级饰品材料</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>南方矿区</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 微透明</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Ore.ShoushanStone</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>寿山石</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>印章/雕件材料</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>福建寿山</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 彩石</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gem.CatsEye</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>猫眼石</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>镶嵌用宝石</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 稀有宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gem.Diamond</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>金刚石</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>顶级镶嵌宝石</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>西域</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 硬度最高</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gem.Lapis</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>青金石</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>蓝色宝石</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>阿富汗</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 古代珍品</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gem.Obsidian</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>黑曜石</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>暗属性宝石</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>火山地区</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 辟邪之石</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Core.Gem.DushanStone</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>独山玉</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>南阳特产</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>河南独山</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 多色玉石</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Core.Spirit.StarlightJade</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>星光石</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>注灵材料</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>星空之地</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 蕴含星力</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Core.Spirit.DragonSlumber</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>龙涎石</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>传说注灵材料</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>深海龙宫</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 龙族遗珍</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Core.Spirit.NuwaStone</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>女娲石</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>神话修复材料</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>女娲遗迹</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 补天之石</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Core.Ore.TinOre</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>锡矿石</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>焊接材料</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>锡矿</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Core.Ore.LeadOre</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>铅矿石</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>工业材料</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>铅矿</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Core.Ore.Jadeite</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>翡翠</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>高级饰品</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 翠绿欲滴</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Core.Ore.Ruby</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>红宝石</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>镶嵌宝石</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 鸽血红</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Core.Ore.Emerald</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>祖母绿</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>镶嵌宝石</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>哥伦比亚</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 翠绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Core.Ore.Sapphire</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>蓝宝石</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>镶嵌宝石</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>斯里兰卡</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 皇家蓝</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>持续时间</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>解除方法</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.HotPoison</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>热毒</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3回合</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>每回合-8HP</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>清热药材</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 热邪入体</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.ColdPoison</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>寒毒</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>3回合</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>每回合-5HP,速度-20%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>温阳药材</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 寒邪侵体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.RotPoison</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>腐毒</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4回合</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>每回合-10HP</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>解毒丹</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 腐蚀血肉</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.GuPoison</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>蛊毒</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5回合</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>每回合-3HP,吸收营养</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>牛黄丸</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 蛊虫侵蚀</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.QiFocus</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>聚气</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3回合</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>攻击+25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>自然消散</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 真气凝聚</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.BloodRush</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>血气方刚</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>暴击率+15%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>自然消散</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 气血充盈</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.GoldenBell</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>金钟罩</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>受到伤害-30%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>受到攻击</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 硬气功</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.IronShirt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>铁布衫</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3回合</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>防御+20%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>自然消散</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 横练功夫</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.SwiftWind</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>风步</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>速度+40%,闪避+10%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>受到攻击</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 轻功</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.EagleEye</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>鹰眼</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3回合</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>命中率+20%,暴击伤害+30%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>自然消散</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 目力过人</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Dizziness</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>眩晕</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1回合</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>无法行动</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>受到治疗</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 头目晕眩</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Freeze</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>冰封</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1回合</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>无法行动,受伤+20%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>火系攻击</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 寒冰入体</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Paralysis</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>麻痹</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>速度-50%,攻击停顿</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>活血药材</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 经脉不通</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Blind</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>致盲</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>命中率-50%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>明目丹</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 双目失明</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Silence</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沉默</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>无法使用技能</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>清心丹</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 禁锢内力</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Terror</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>恐惧</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>有30%概率逃跑</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>安神丸</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 心惊胆战</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Burning</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>灼烧</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>每回合-15HP</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>冷水</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 火焰持续</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Bleeding</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>流血</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3回合</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>每回合-5HP,可叠加5层</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>止血草</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 伤口撕裂</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Weakness</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>虚弱</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3回合</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>攻击力-30%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>补气汤</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 体力不支</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Core.Status.Slow</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>迟缓</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2回合</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>速度-30%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>麻黄</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 动作迟缓</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Core.Status.Curse</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>诅咒</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>永久</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>全属性-10%</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>净化符</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 邪术</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Core.Status.Blessing</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>祝福</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>5回合</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>全属性+15%</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>自然消散</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 神佑</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Core.Status.Invincible</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>金刚不坏</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>1回合</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>免疫所有伤害</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>受到攻击</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 至高防御</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12404,6 +14842,4276 @@
       <c r="K23" s="4" t="inlineStr">
         <is>
           <t>[拓展] 拓展设计 - 消耗生命换取力量</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>防御</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>掉落</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.FoxSpirit</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>狐妖</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>妖兽</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>妖核×2,金币×50</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 九尾妖狐眷族</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.WhiteFox</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>白狐</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>妖兽</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>狐毛×3,金币×30</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 灵性极高</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.SnakeSpirit</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>蛇妖</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>妖兽</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>蛇胆×2,金币×60</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 修炼成精</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.Ghost</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>孤魂野鬼</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>鬼魂</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>幽魂×1,金币×20</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 怨念不散</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.FierceGhost</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>厉鬼</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>鬼魂</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>厉魂×2,金币×100</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 含冤而死</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.Zombie</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>跳尸</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>僵尸</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>僵尸心×1,金币×80</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 白僵进化</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.TreeSpirit</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>树妖</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>精怪</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>千年古木×1,金币×120</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 草木成精</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.JadeBear</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>玉麒麟</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>神兽</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>麒麟角×1,金币×500</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 祥瑞之兽</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.Bandit</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>山贼</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>匪徒</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>朴刀×1,金币×25</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 占山为王</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.RogueLeader</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>草寇头目</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>匪徒</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>皮甲×1,金币×60</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 小股势力</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster流动寇</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>流寇</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>匪徒</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>金币×40,随机物品</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 流窜作案</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.LocalBully</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>恶霸</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>匪徒</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>保护费×100,金币×80</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 地方一霸</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.Asura</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>修罗</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>神话</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>修罗之血×1,金币×300</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 阿修罗族</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.Yaksha</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>夜叉</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>神话</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>夜叉皮×1,金币×250</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 鬼怪生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Core.Monster.Rakshasa</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>罗刹</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>神话</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>罗刹之牙×1,金币×350</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 恶鬼</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Core.Monster.Scorpion</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>毒蝎</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>妖兽</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>蝎尾×2,金币×25</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 沙漠</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Core.Monster.Mantis</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>螳螂精</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>妖兽</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>螳臂×1,金币×40</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 速度快</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Core.Monster.Spider</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>蛛妖</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>妖兽</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>蛛丝×3,金币×70</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 吐丝束缚</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Core.Monster.WolfKing</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>狼王</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>妖兽</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>狼牙×2,金币×150</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 群狼首领</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Core.Monster.BlackTortoise</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>玄龟</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>神兽</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>龟甲×2,金币×200</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 极高防御</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Core.Monster.Qilin</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>麒麟</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>神兽</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>麒麟鳞×2,金币×800</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 祥瑞</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>职业</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.SimpleBlade</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>朴刀</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>刀</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 基础武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.BroadBlade</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>戒刀</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>刀</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>暴击+5%</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 佛门武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.MoonBlade</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>偃月刀</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>刀</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>范围伤害+10%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>镖师</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 长柄大刀</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.DragonSaber</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>龙牙刀</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>刀</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>对龙系伤害+30%</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 传说武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.ShortSword</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>短剑</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>速度+10%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 入门剑器</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.LongSword</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>长剑</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 标准武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.FineSword</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>精钢剑</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>破甲+5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>镖师</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 精制武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.SpiritSword</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>灵剑</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>内力加成+15%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>学者</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 蕴含灵气</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.FrostBlade</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>寒冰剑</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>冰冻几率15%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 冰系附魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.Spear</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>长枪</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>枪</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>攻击距离+1</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>镖师</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 基础枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.Halberd</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>戟</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>枪</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>刺穿+10%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>镖师</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战阵武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.DragonHalberd</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>龙戟</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>枪</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>对BOSS伤害+25%</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>将军</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战场之王</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.FoldingFan</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>折扇</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>扇</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>敏捷+5%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>商贾</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 文人武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.WarFan</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>羽扇</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>扇</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>技能冷却-10%</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>智者</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 诸葛亮之扇</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Core.Weapon.ImmortalFan</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>仙羽扇</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>扇</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全体攻击+20%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>医者</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 仙家之物</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Core.Weapon.Pudao</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>扑刀</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>刀</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>连击+1</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>镖师</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 快刀</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Core.Weapon.WhipSword</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>鞭剑</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>灵活连击</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 软剑</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Core.Weapon.DoubleSword</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>双剑</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>双倍攻击次数</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 双武</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Core.Weapon.ThreeSection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>三节棍</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>棍</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>击晕几率10%</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>镖师</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 软兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Core.Weapon.Staff</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>法杖</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>杖</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>技能伤害+25%</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>医者</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 法师武器</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>防御</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>速度惩罚</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.ClothRobe</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>布衣</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>布甲</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>魔抗+3</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 基础防具</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.SilkRobe</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>绸袍</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>布甲</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>魔抗+8,魅力+2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 商人常服</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.TaoistRobe</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>道袍</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>布甲</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>内力回复+20%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 道士装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.LeatherArmor</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>皮甲</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>轻甲</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 基础轻甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.HardLeather</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>硬皮甲</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>轻甲</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>防御+5</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 正规军装</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.JadeLeather</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>玉皮甲</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>轻甲</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>所有抗性+10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 精良皮甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.ChainMail</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>锁子甲</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>中甲</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 基础中甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.IronChainMail</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>铁锁甲</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>中甲</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>格挡+10%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 正规军备</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.SilverChainMail</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>银锁甲</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>中甲</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>圣光抗性+20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 骑士标配</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.PlateArmor</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>板甲</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>重甲</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>免疫穿刺</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 重装战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.DragonScale</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>龙鳞甲</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>重甲</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>火抗+50,HP+100</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 龙鳞打造</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Core.Armor.HeavenlyArmor</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>天将甲</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>重甲</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全属性+10%,无敌1秒/次</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 神话级防具</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Core.Armor.BambooArmor</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>竹甲</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>轻甲</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>轻便+5%速度</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 丛林</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Core.Armor.ScaledArmor</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>鳞甲</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>中甲</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>穿刺抗性+15</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 爬行类</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Core.Armor.MirrorArmor</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>明光铠</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>重甲</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>反弹伤害15%</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 镜面反射</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Core.Armor.GhostShroud</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>幽魂披风</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>布甲</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>闪避+20%,暗属性</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 鬼魅</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>事件ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>节点ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>节点类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>选项数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>结局数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.EventTree.MerchantEncounter</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>node_1~node_5</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>路遇商队</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>旅行途中遇到商队,选择交易或离开</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 经典分支叙事</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.EventTree.AncientRuins</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>node_1~node_6</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>神秘遗迹</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>探索古代遗迹,可能发现宝藏或陷阱</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 探险分支叙事</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.EventTree.InnRest</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>node_1~node_4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>路旁旅店</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>旅途疲惫,在旅店休息或继续前进</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 休息分支叙事</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Core.EventTree.MysteriousMonk</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>node_1~node_6</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>神秘僧人</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>拓展设计 - 路遇神秘僧人,可获得佛法加持或修行任务</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 佛门事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Core.EventTree.DragonPool</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>node_1~node_8</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Root/Random/Choice/End</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>龙潭探宝</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>拓展设计 - 传说龙潭,可能有真龙宝藏或龙族惩罚</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 神话事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Core.EventTree.TeaHouse</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>node_1~node_5</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>茶馆奇遇</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>拓展设计 - 古镇茶馆,听书了解秘密或遇到江湖人士</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 江湖事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Core.EventTree.MedicineValley</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>node_1~node_7</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>药王谷</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>拓展设计 - 误入药王谷,可采药或需解毒</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 医药事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Core.EventTree.OverthrowBandits</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>node_1~node_6</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>剿灭山贼</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>拓展设计 - 官兵请求协助剿匪,战斗与外交选择</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 战斗事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Core.EventTree.GhostCity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>node_1~node_9</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Root/Choice/Random/End</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>鬼城迷踪</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>拓展设计 - 进入无人鬼城,探索真相或逃离</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 鬼魂事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Core.EventTree.ImperialExam</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>node_1~node_7</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Root/Choice/End</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>赶考书生</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>拓展设计 - 遇见赶考书生,可结伴或帮助</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 书生事件</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>产地</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>收购价</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>出售价</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>利润%</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>需求季节</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Salt</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>食盐</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>盐井</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 生活必需品</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Rice</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>大米</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>稻田</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 主食</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Wheat</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>麦田</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>秋季</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 制作面粉</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Silk</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>丝绸</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>江南</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120%</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 丝绸之路核心</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Tea</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>茶叶</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>茶山</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 茶马古道</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Porcelain</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>瓷器</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>景德镇</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>167%</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 外销主力</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Incense</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>香料</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>西域</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 香料之路</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Cinnamon</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>肉桂</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>南方</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>133%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 调味料</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.StarAnise</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>八角</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>南方</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>120%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>秋季</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 炖肉调料</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Medicine</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>药材</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>各大药铺</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140%</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 医商必备</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Trade.Ginseng</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>人参</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>长白山</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>秋季</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 高档药材</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Core.Trade.Antique</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>古董</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>遗迹</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>不定</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 鉴定价值</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Core.Trade.Jade</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>玉石</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 奢侈品</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Core.Trade.Horse</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>马匹</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>草原</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 坐骑</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Core.Trade.Paper</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>纸张</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>造纸坊</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 文人需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Core.Trade.Bamboo</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>竹简</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>竹林</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>167%</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 记录工具</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Core.Trade.Vine</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>藤蔓</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>南方</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 编织材料</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>地点ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>特产</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.ChangAn</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>长安城</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>都城</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>关中</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>丝绸,瓷器,古籍</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>科举,庙会,灯会</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 大唐都城</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.LuoYang</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>洛阳城</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>都城</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>中原</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>牡丹,古籍,药材</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>花会,佛会</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 千年帝都</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.HangZhou</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>杭州城</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>商城</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>江南</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>茶叶,丝绸,龙井</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>船宴,观潮</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 人间天堂</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.SuZhou</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>苏州城</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>商城</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>江南</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>丝绸,刺绣,园林</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>评弹,昆曲</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 江南水乡</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.YangZhou</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>扬州城</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>商城</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>江南</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>盐业,玉石,美食</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>盐商,瘦马</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 淮左名都</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.JingZhou</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>荆州城</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>重镇</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>铁器,木材</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>三国遗迹</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 兵家必争</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.XianYang</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>咸阳城</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>古镇</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>关中</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>农产品,皮草</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>秦腔,古迹</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 秦朝故都</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.KaiFeng</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>开封府</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>都城</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>中原</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>美食,汴绣</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>小吃,夜市</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 北宋汴京</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.JadePass</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>玉门关</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>关卡</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>西域</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>玉石,香料</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>丝路商队</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 西域门户</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.Yulin</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>榆林</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>边塞</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>塞北</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>战马,皮草,人参</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>游牧交易</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 塞外江南</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Core.Place.DuYan</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>敦煌</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>要塞</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>西域</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>壁画,佛像,绢画</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>石窟艺术</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 丝路明珠</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Core.Place.MountWu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>武夷山</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>山脉</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>江南</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>茶叶,草药</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>采茶体验</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 名山</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Core.Place.TaiShan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>泰山</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>山脉</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>石碑,药材</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>封禅大典</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 五岳之首</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Core.Place.WestLake</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>西湖</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>湖泊</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>江南</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>莲藕,鲤鱼,龙井</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>画舫游湖</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 人间仙境</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Core.Place.QinLing</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>秦岭</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>山脉</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>关中</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>珍禽,异兽,矿石</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>深山探险</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 天然宝库</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Core.Place.LiaoDong</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>辽东</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>边疆</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>东北</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>人参,貂皮,矿石</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>游牧交易</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>[拓展] 拓展设计 - 塞外</t>
         </is>
       </c>
     </row>
